--- a/data/trans_orig/RUIDO_1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>815</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>934</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>17226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35852</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40712</t>
+          <t>41334</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107833</t>
+          <t>108248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135414</t>
+          <t>135463</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129095</t>
+          <t>130243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145234</t>
+          <t>144941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>247859</t>
+          <t>245454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>278644</t>
+          <t>278378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>31624</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33665</t>
+          <t>30020</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25721</t>
+          <t>28015</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35998</t>
+          <t>34739</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12998</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42503</t>
+          <t>40015</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8632</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21592</t>
+          <t>21267</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25493</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56096</t>
+          <t>55760</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25214</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>18071</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33119</t>
+          <t>34552</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>181424</t>
+          <t>185778</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>224405</t>
+          <t>224499</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>173224</t>
+          <t>172575</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>198516</t>
+          <t>197643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>365751</t>
+          <t>367312</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>412377</t>
+          <t>413662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>950</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>171</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15408</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>13587</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>33357</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38998</t>
+          <t>39641</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>23760</t>
+          <t>24438</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>44174</t>
+          <t>43657</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>47723</t>
+          <t>46452</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>75534</t>
+          <t>75651</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>129679</t>
+          <t>130361</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>154255</t>
+          <t>154985</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>125353</t>
+          <t>124145</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>146440</t>
+          <t>145822</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>263040</t>
+          <t>262306</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>294377</t>
+          <t>295630</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>9048</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>343</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>23628</t>
+          <t>23659</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>12411</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>130319</t>
+          <t>112369</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>146557</t>
+          <t>153472</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>18083</t>
+          <t>20798</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>301</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>18508</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>28987</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>28411</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>24207</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>51146</t>
+          <t>53646</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>105535</t>
+          <t>107446</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>136306</t>
+          <t>137693</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>83452</t>
+          <t>93234</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>181145</t>
+          <t>182322</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>198793</t>
+          <t>194276</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>305468</t>
+          <t>306535</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6283,12 +6283,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6333,12 +6333,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6396,12 +6396,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6559,12 +6559,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6848,12 +6848,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>44810</t>
+          <t>46110</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>62482</t>
+          <t>61950</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>52386</t>
+          <t>52359</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>67673</t>
+          <t>67989</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>102648</t>
+          <t>103479</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>125448</t>
+          <t>125379</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,18%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>36752</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>53512</t>
+          <t>52896</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>56134</t>
+          <t>56124</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>72287</t>
+          <t>71279</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>96871</t>
+          <t>96785</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>120074</t>
+          <t>119147</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,49%</t>
         </is>
       </c>
     </row>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7545,12 +7545,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7643,12 +7643,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7756,12 +7756,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7869,12 +7869,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7982,12 +7982,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7997,12 +7997,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8017,12 +8017,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8095,12 +8095,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>456</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>855</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -8434,12 +8434,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>8981</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>12726</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>19577</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8547,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>28741</t>
+          <t>28941</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>22104</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>24122</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>44454</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>103560</t>
+          <t>102833</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>121298</t>
+          <t>120667</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>106068</t>
+          <t>105954</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>122215</t>
+          <t>122402</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>215141</t>
+          <t>215576</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>239809</t>
+          <t>239129</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -8890,12 +8890,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -9003,12 +9003,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -9116,12 +9116,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>787</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -9229,12 +9229,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9244,12 +9244,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>390</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -9342,12 +9342,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>17699</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>25035</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -9455,12 +9455,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>11778</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>19599</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>13686</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>22414</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>28326</t>
+          <t>29268</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>9342</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>21377</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>26421</t>
+          <t>25830</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>21482</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>41650</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>22867</t>
+          <t>23306</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9922,12 +9922,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>48784</t>
+          <t>45990</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>59490</t>
+          <t>59367</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>197826</t>
+          <t>199829</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>227987</t>
+          <t>230995</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10035,12 +10035,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>363863</t>
+          <t>363323</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>471104</t>
+          <t>470675</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>579283</t>
+          <t>578595</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>711442</t>
+          <t>710540</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -10250,12 +10250,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10265,12 +10265,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10363,12 +10363,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10378,12 +10378,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10398,12 +10398,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10413,12 +10413,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10476,12 +10476,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10491,12 +10491,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10511,12 +10511,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10526,12 +10526,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10589,12 +10589,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10659,12 +10659,12 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10928,12 +10928,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -11041,12 +11041,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>729</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -11267,12 +11267,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>42681</t>
+          <t>43321</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>68384</t>
+          <t>69009</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>24326</t>
+          <t>23953</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>41671</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>73286</t>
+          <t>72255</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>102208</t>
+          <t>102345</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -11380,12 +11380,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>264953</t>
+          <t>265227</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>292194</t>
+          <t>293255</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>288288</t>
+          <t>287917</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>306447</t>
+          <t>306444</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11450,12 +11450,12 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>558876</t>
+          <t>560770</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>592813</t>
+          <t>593031</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -11610,12 +11610,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>13227</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11680,12 +11680,12 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>26502</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -11723,12 +11723,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -11738,12 +11738,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>33378</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -11836,12 +11836,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11871,12 +11871,12 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -11949,12 +11949,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -11984,12 +11984,12 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -12062,12 +12062,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>25575</t>
+          <t>24974</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>41402</t>
+          <t>41985</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -12175,12 +12175,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>40562</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12210,12 +12210,12 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>17274</t>
+          <t>17883</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12245,12 +12245,12 @@
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>49739</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -12288,12 +12288,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>19410</t>
+          <t>18591</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>49238</t>
+          <t>50759</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>36493</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>219719</t>
+          <t>188811</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -12338,12 +12338,12 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12358,12 +12358,12 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>65841</t>
+          <t>65088</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>222454</t>
+          <t>259745</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -12401,12 +12401,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>50961</t>
+          <t>46900</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>24890</t>
+          <t>24483</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -12451,12 +12451,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>37181</t>
+          <t>37468</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>67932</t>
+          <t>67960</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
@@ -12514,12 +12514,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>70481</t>
+          <t>71986</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>123487</t>
+          <t>121176</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -12529,12 +12529,12 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -12549,12 +12549,12 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>50614</t>
+          <t>52719</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>90751</t>
+          <t>90402</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12584,12 +12584,12 @@
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>130996</t>
+          <t>130783</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>198483</t>
+          <t>200021</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -12627,12 +12627,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>163434</t>
+          <t>164745</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>214241</t>
+          <t>218285</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -12642,12 +12642,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -12662,12 +12662,12 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>126074</t>
+          <t>129541</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>213934</t>
+          <t>213533</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -12677,12 +12677,12 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -12697,12 +12697,12 @@
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>301026</t>
+          <t>303378</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>413309</t>
+          <t>412655</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -12740,12 +12740,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>1208325</t>
+          <t>1204150</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>1287758</t>
+          <t>1291266</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -12755,12 +12755,12 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>1434953</t>
+          <t>1435429</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1631081</t>
+          <t>1623612</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -12790,12 +12790,12 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>2679933</t>
+          <t>2672528</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>2910240</t>
+          <t>2904034</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>884</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>472</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,67 +1212,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4458</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>9414</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4427</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1796</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>10149</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>496</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1403,22 +1403,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1516,32 +1516,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1551,32 +1551,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>11195</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30924</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41334</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>125527</t>
+          <t>135857</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108248</t>
+          <t>124716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135463</t>
+          <t>143782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>138536</t>
+          <t>151180</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130243</t>
+          <t>143093</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144941</t>
+          <t>157559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>264063</t>
+          <t>287037</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>245454</t>
+          <t>274136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>278378</t>
+          <t>299626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,63%</t>
         </is>
       </c>
     </row>
@@ -1968,17 +1968,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>157176</t>
+          <t>164558</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>157176</t>
+          <t>164558</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>157176</t>
+          <t>164558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>163318</t>
+          <t>177352</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>163318</t>
+          <t>177352</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>163318</t>
+          <t>177352</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>320494</t>
+          <t>341910</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>320494</t>
+          <t>341910</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>320494</t>
+          <t>341910</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2095,12 +2095,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10828</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2537,32 +2537,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,32 +2572,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,22 +2607,22 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>13512</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2650,32 +2650,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31624</t>
+          <t>25988</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,32 +2720,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>12890</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30020</t>
+          <t>29399</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>19651</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>17542</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34739</t>
+          <t>31978</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -2876,22 +2876,22 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>17454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11261</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>10705</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>22505</t>
+          <t>21290</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23305</t>
+          <t>23602</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40015</t>
+          <t>39863</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14016</t>
+          <t>15269</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21267</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>37320</t>
+          <t>38871</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>27452</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55760</t>
+          <t>56319</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24024</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18071</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -3215,32 +3215,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>205530</t>
+          <t>206721</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>185778</t>
+          <t>184173</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>224499</t>
+          <t>224542</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>187220</t>
+          <t>198117</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>172575</t>
+          <t>185095</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>197643</t>
+          <t>208766</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>392750</t>
+          <t>404838</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>367312</t>
+          <t>382104</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>413662</t>
+          <t>425856</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -3328,17 +3328,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>272340</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>272340</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>272340</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>233994</t>
+          <t>246871</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>233994</t>
+          <t>246871</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>233994</t>
+          <t>246871</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>506334</t>
+          <t>519813</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>506334</t>
+          <t>519813</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>506334</t>
+          <t>519813</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>979</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>979</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>912</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>20470</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8836</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15122</t>
+          <t>15935</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>20852</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>32633</t>
+          <t>32892</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -4462,32 +4462,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>27552</t>
+          <t>26499</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>39641</t>
+          <t>37143</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4497,32 +4497,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>32864</t>
+          <t>32287</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>43657</t>
+          <t>43721</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>60416</t>
+          <t>58786</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>45357</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>75651</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -4575,32 +4575,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>143161</t>
+          <t>146913</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>130361</t>
+          <t>134095</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>154985</t>
+          <t>158512</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4610,32 +4610,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>136593</t>
+          <t>142257</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>124145</t>
+          <t>130433</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>145822</t>
+          <t>152075</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>279754</t>
+          <t>289170</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>262306</t>
+          <t>271558</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>295630</t>
+          <t>305756</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -4688,17 +4688,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>186803</t>
+          <t>189949</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>186803</t>
+          <t>189949</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>186803</t>
+          <t>189949</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>181412</t>
+          <t>187099</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>181412</t>
+          <t>187099</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>181412</t>
+          <t>187099</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>368216</t>
+          <t>377049</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>368216</t>
+          <t>377049</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>368216</t>
+          <t>377049</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4850,12 +4850,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,32 +4875,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12522</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5292,22 +5292,22 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>341</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,22 +5327,22 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>757</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>24451</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>46743</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12411</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>112369</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>54603</t>
+          <t>23992</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>153472</t>
+          <t>44468</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -5596,32 +5596,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>20798</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5631,32 +5631,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>354</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>18508</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>20866</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>11066</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>28987</t>
+          <t>35435</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5744,32 +5744,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>19572</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>28411</t>
+          <t>30549</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>36536</t>
+          <t>42348</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>31256</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>53646</t>
+          <t>61497</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -5822,32 +5822,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>9058</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5857,32 +5857,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>13891</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>123232</t>
+          <t>143871</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>107446</t>
+          <t>124169</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>137693</t>
+          <t>158284</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>151967</t>
+          <t>172251</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>93234</t>
+          <t>159066</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>182322</t>
+          <t>182871</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>275199</t>
+          <t>316122</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>194276</t>
+          <t>292611</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>306535</t>
+          <t>335084</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -6048,17 +6048,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>171180</t>
+          <t>198685</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>171180</t>
+          <t>198685</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>171180</t>
+          <t>198685</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6083,17 +6083,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>229157</t>
+          <t>220453</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>229157</t>
+          <t>220453</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>229157</t>
+          <t>220453</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>400337</t>
+          <t>419138</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>400337</t>
+          <t>419138</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>400337</t>
+          <t>419138</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>401</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>728</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>455</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -7069,32 +7069,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7104,32 +7104,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7139,32 +7139,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>13135</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -7182,32 +7182,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>54106</t>
+          <t>58570</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>61950</t>
+          <t>67907</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7217,32 +7217,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>60446</t>
+          <t>65235</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>52359</t>
+          <t>56491</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>67989</t>
+          <t>73199</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>114551</t>
+          <t>123806</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>103479</t>
+          <t>111725</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>125379</t>
+          <t>134878</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -7295,32 +7295,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>49413</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>36752</t>
+          <t>40452</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>52896</t>
+          <t>58207</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7330,32 +7330,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>63659</t>
+          <t>68324</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>56124</t>
+          <t>60420</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>71279</t>
+          <t>76879</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>107804</t>
+          <t>117738</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>96785</t>
+          <t>106099</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>119147</t>
+          <t>129739</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,52%</t>
         </is>
       </c>
     </row>
@@ -7408,17 +7408,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>102774</t>
+          <t>113244</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>102774</t>
+          <t>113244</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>102774</t>
+          <t>113244</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>128622</t>
+          <t>138580</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>128622</t>
+          <t>138580</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>128622</t>
+          <t>138580</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>231396</t>
+          <t>251825</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>231396</t>
+          <t>251825</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>231396</t>
+          <t>251825</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>498</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>489</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -8316,22 +8316,22 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>851</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>626</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8386,22 +8386,22 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -8429,32 +8429,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8464,27 +8464,27 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>12972</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12316</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>19632</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -8542,32 +8542,32 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>18550</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>28941</t>
+          <t>26860</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8577,32 +8577,32 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>22104</t>
+          <t>22456</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8612,32 +8612,32 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>33748</t>
+          <t>32676</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>24607</t>
+          <t>24408</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>44931</t>
+          <t>44378</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -8655,32 +8655,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>112848</t>
+          <t>112693</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>102833</t>
+          <t>103286</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>120667</t>
+          <t>119890</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8690,32 +8690,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>115671</t>
+          <t>118672</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>105954</t>
+          <t>109747</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>122402</t>
+          <t>126081</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>228519</t>
+          <t>231365</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>215576</t>
+          <t>218838</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>239129</t>
+          <t>241291</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -8768,17 +8768,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>141212</t>
+          <t>139964</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>141212</t>
+          <t>139964</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>141212</t>
+          <t>139964</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8803,17 +8803,17 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>140382</t>
+          <t>143274</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>140382</t>
+          <t>143274</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>140382</t>
+          <t>143274</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8838,17 +8838,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>281594</t>
+          <t>283238</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>281594</t>
+          <t>283238</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>281594</t>
+          <t>283238</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8885,32 +8885,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8955,32 +8955,32 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -8998,32 +8998,32 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9033,32 +9033,32 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>11748</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9068,32 +9068,32 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -9111,32 +9111,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -9156,12 +9156,12 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9181,32 +9181,32 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -9259,32 +9259,32 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9294,32 +9294,32 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -9337,32 +9337,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9372,32 +9372,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>17404</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>13957</t>
+          <t>16267</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>24661</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -9450,32 +9450,32 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9485,32 +9485,32 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9520,32 +9520,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>19525</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -9563,32 +9563,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>13830</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9598,32 +9598,32 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>13391</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9633,32 +9633,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>17687</t>
+          <t>21407</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>29268</t>
+          <t>31530</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -9676,32 +9676,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>17447</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9711,32 +9711,32 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9746,32 +9746,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>22480</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -9789,32 +9789,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>19856</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>25830</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9824,32 +9824,32 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>19757</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9859,32 +9859,32 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>39613</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>41650</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -9902,32 +9902,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>23306</t>
+          <t>29253</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9937,32 +9937,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>29909</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>20431</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>45990</t>
+          <t>43494</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9972,32 +9972,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>37997</t>
+          <t>48068</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>37048</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>59367</t>
+          <t>63996</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -10015,32 +10015,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>215544</t>
+          <t>238917</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>199829</t>
+          <t>220664</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>230995</t>
+          <t>256412</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10050,32 +10050,32 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>423244</t>
+          <t>262104</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>363323</t>
+          <t>244393</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>470675</t>
+          <t>275557</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10085,32 +10085,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>638788</t>
+          <t>501022</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>578595</t>
+          <t>473737</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>710540</t>
+          <t>523159</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -10128,17 +10128,17 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>280830</t>
+          <t>321543</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>280830</t>
+          <t>321543</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>280830</t>
+          <t>321543</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10163,17 +10163,17 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>497060</t>
+          <t>357024</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>497060</t>
+          <t>357024</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>497060</t>
+          <t>357024</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10198,17 +10198,17 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>777890</t>
+          <t>678568</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>777890</t>
+          <t>678568</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>777890</t>
+          <t>678568</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>973</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -10968,12 +10968,12 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>973</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V94" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>608</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>608</t>
         </is>
       </c>
       <c r="S95" s="2" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -11149,32 +11149,32 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>17760</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11184,32 +11184,32 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>812</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11219,32 +11219,32 @@
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -11262,32 +11262,32 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>54427</t>
+          <t>60172</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>43321</t>
+          <t>47484</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>69009</t>
+          <t>76850</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11297,17 +11297,17 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>31809</t>
+          <t>36758</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>23953</t>
+          <t>27281</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>47650</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11332,32 +11332,32 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>86237</t>
+          <t>96930</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>72255</t>
+          <t>80026</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>102345</t>
+          <t>115872</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -11375,32 +11375,32 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>280082</t>
+          <t>330985</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>265227</t>
+          <t>314153</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>293255</t>
+          <t>344822</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11410,32 +11410,32 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>297689</t>
+          <t>344357</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>287917</t>
+          <t>333779</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>306444</t>
+          <t>354810</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11445,32 +11445,32 @@
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>577772</t>
+          <t>675342</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>560770</t>
+          <t>655698</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>593031</t>
+          <t>692937</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,16%</t>
         </is>
       </c>
     </row>
@@ -11488,17 +11488,17 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>342719</t>
+          <t>400188</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>342719</t>
+          <t>400188</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>342719</t>
+          <t>400188</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11523,17 +11523,17 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>333849</t>
+          <t>385827</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>333849</t>
+          <t>385827</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>333849</t>
+          <t>385827</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -11558,17 +11558,17 @@
       </c>
       <c r="R99" s="2" t="inlineStr">
         <is>
-          <t>676569</t>
+          <t>786015</t>
         </is>
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>676569</t>
+          <t>786015</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>676569</t>
+          <t>786015</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -11605,32 +11605,32 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>20999</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11640,32 +11640,32 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11675,32 +11675,32 @@
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>16426</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>26465</t>
+          <t>30374</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -11718,32 +11718,32 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11753,32 +11753,32 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>16392</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11788,32 +11788,32 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>33378</t>
+          <t>37994</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -11831,32 +11831,32 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11866,32 +11866,32 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11901,32 +11901,32 @@
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -11979,32 +11979,32 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12014,17 +12014,17 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>718</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -12057,67 +12057,67 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15378</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>25418</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>16609</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>10283</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>25735</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>14436</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>8655</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>22806</t>
-        </is>
-      </c>
-      <c r="N104" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12127,32 +12127,32 @@
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>29132</t>
+          <t>31987</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>22236</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>41985</t>
+          <t>44226</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -12170,32 +12170,32 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>39914</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12205,32 +12205,32 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12240,32 +12240,32 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>30308</t>
+          <t>29642</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>51708</t>
+          <t>45832</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -12283,32 +12283,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>18591</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>50759</t>
+          <t>54062</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12318,22 +12318,22 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>74209</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>188811</t>
+          <t>62424</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12353,32 +12353,32 @@
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>105131</t>
+          <t>79792</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>65088</t>
+          <t>61259</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>259745</t>
+          <t>105655</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -12396,32 +12396,32 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>23169</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>46900</t>
+          <t>51769</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -12431,32 +12431,32 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>10040</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>24483</t>
+          <t>26971</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12466,32 +12466,32 @@
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>50184</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>37468</t>
+          <t>40691</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>67960</t>
+          <t>71851</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -12509,32 +12509,32 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>92646</t>
+          <t>99664</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>71986</t>
+          <t>76745</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>121176</t>
+          <t>125156</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -12544,32 +12544,32 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>73667</t>
+          <t>87540</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>52719</t>
+          <t>73669</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>90402</t>
+          <t>104752</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12579,32 +12579,32 @@
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>166314</t>
+          <t>187204</t>
         </is>
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>130783</t>
+          <t>161253</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>200021</t>
+          <t>217540</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -12622,32 +12622,32 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>188942</t>
+          <t>201737</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>164745</t>
+          <t>175067</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>218285</t>
+          <t>228300</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -12657,32 +12657,32 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>181557</t>
+          <t>197074</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>129541</t>
+          <t>175469</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>213533</t>
+          <t>223696</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -12692,32 +12692,32 @@
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>370499</t>
+          <t>398811</t>
         </is>
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>303378</t>
+          <t>364533</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>412655</t>
+          <t>435574</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -12735,32 +12735,32 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>1250069</t>
+          <t>1365372</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>1204150</t>
+          <t>1320587</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>1291266</t>
+          <t>1407764</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -12770,32 +12770,32 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>1514580</t>
+          <t>1457263</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>1435429</t>
+          <t>1424488</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1623612</t>
+          <t>1486307</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -12805,32 +12805,32 @@
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>2764650</t>
+          <t>2822634</t>
         </is>
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>2672528</t>
+          <t>2772875</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>2904034</t>
+          <t>2873058</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -12848,17 +12848,17 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -12883,17 +12883,17 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -12918,17 +12918,17 @@
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">

--- a/data/trans_orig/RUIDO_1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del ruido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
